--- a/data/labour-market/Employment rate/employment_rate_by_constituency_11022026.xlsx
+++ b/data/labour-market/Employment rate/employment_rate_by_constituency_11022026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/files/IPR/Centres/Brunel Centre/Labour Market/Employment_rate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\IPR\Centres\Brunel Centre\Labour Market\Employment_rate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F312F193-36F0-8B42-8001-7EE7BD11CE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E8701B-AB6A-42E1-869C-43E99500EF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2840" yWindow="-21100" windowWidth="35740" windowHeight="20400" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
   <si>
     <t>annual population survey</t>
   </si>
@@ -151,6 +151,60 @@
   </si>
   <si>
     <t>employment_rate</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>Office for National Statistics (ONS)</t>
+  </si>
+  <si>
+    <t>ONS dataset</t>
+  </si>
+  <si>
+    <t>Annual population survey (ONS)</t>
+  </si>
+  <si>
+    <t>ONS tables</t>
+  </si>
+  <si>
+    <t>ONS publication date</t>
+  </si>
+  <si>
+    <t>Sep 2025</t>
+  </si>
+  <si>
+    <t>Next ONS update</t>
+  </si>
+  <si>
+    <t>ONS link</t>
+  </si>
+  <si>
+    <t>https://www.nomisweb.co.uk/datasets/apsnew</t>
+  </si>
+  <si>
+    <t>Created date</t>
+  </si>
+  <si>
+    <t>Last updated</t>
+  </si>
+  <si>
+    <t>Geography used for analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggregation method  </t>
+  </si>
+  <si>
+    <t>Aggregated by NOMIS</t>
+  </si>
+  <si>
+    <t>Data information:</t>
+  </si>
+  <si>
+    <t>A residence based labour market survey encompassing population, economic activity (employment and unemployment), economic inactivity and qualifications. These are broken down where possible by gender, age, ethnicity, industry and occupation. Available at Local Authority level and above. Updated quarterly.</t>
+  </si>
+  <si>
+    <t>The Greater West of England parliamentary constituencies</t>
   </si>
 </sst>
 </file>
@@ -158,9 +212,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -234,6 +288,22 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -252,10 +322,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -276,22 +347,34 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -624,9 +707,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95BD1EC-4DA4-5A44-84AC-AA1007456D02}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.453125" customWidth="1"/>
+    <col min="2" max="2" width="58.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="12"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="15">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.4">
+      <c r="A6" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="17">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="17"/>
+    </row>
+    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -634,23 +806,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1" collapsed="1"/>
     <col min="2" max="5" width="14" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -658,7 +830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -666,18 +838,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-    </row>
-    <row r="8" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
@@ -691,7 +863,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -708,7 +880,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
@@ -725,7 +897,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>14</v>
       </c>
@@ -742,7 +914,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
@@ -759,7 +931,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
@@ -776,7 +948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
@@ -793,7 +965,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>18</v>
       </c>
@@ -810,7 +982,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
@@ -827,7 +999,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>20</v>
       </c>
@@ -844,7 +1016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>21</v>
       </c>
@@ -861,7 +1033,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
@@ -878,7 +1050,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>23</v>
       </c>
@@ -895,7 +1067,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>24</v>
       </c>
@@ -912,7 +1084,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>25</v>
       </c>
@@ -929,7 +1101,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>26</v>
       </c>
@@ -946,7 +1118,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>27</v>
       </c>
@@ -963,7 +1135,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>28</v>
       </c>
@@ -980,7 +1152,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>29</v>
       </c>
@@ -997,7 +1169,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>30</v>
       </c>
@@ -1014,7 +1186,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>31</v>
       </c>
@@ -1031,7 +1203,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
@@ -1048,7 +1220,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>33</v>
       </c>
@@ -1065,7 +1237,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>34</v>
       </c>
@@ -1082,7 +1254,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>35</v>
       </c>
@@ -1099,7 +1271,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>36</v>
       </c>
@@ -1116,7 +1288,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>37</v>
       </c>
@@ -1133,7 +1305,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>38</v>
       </c>
@@ -1150,7 +1322,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>39</v>
       </c>
@@ -1167,7 +1339,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
         <v>40</v>
       </c>
@@ -1183,13 +1355,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFEFC44B-79E9-F44C-8230-3ABF91284FAC}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -1197,7 +1369,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
@@ -1205,7 +1377,7 @@
         <v>73.7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
@@ -1213,7 +1385,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
@@ -1221,7 +1393,7 @@
         <v>76.400000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -1229,7 +1401,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
@@ -1237,7 +1409,7 @@
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
@@ -1245,7 +1417,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
@@ -1253,7 +1425,7 @@
         <v>76.3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
@@ -1261,7 +1433,7 @@
         <v>82.9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
@@ -1269,7 +1441,7 @@
         <v>78.599999999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
@@ -1277,7 +1449,7 @@
         <v>85.4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
@@ -1285,7 +1457,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>23</v>
       </c>
@@ -1293,7 +1465,7 @@
         <v>90.9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>24</v>
       </c>
@@ -1301,7 +1473,7 @@
         <v>84.4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>25</v>
       </c>
@@ -1309,7 +1481,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>26</v>
       </c>
@@ -1317,7 +1489,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>27</v>
       </c>
@@ -1325,7 +1497,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>28</v>
       </c>
@@ -1333,7 +1505,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>29</v>
       </c>
@@ -1341,7 +1513,7 @@
         <v>80.5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>30</v>
       </c>
@@ -1349,7 +1521,7 @@
         <v>80.599999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>31</v>
       </c>
@@ -1357,7 +1529,7 @@
         <v>82.3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>32</v>
       </c>
@@ -1365,7 +1537,7 @@
         <v>79.099999999999994</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>33</v>
       </c>
@@ -1373,7 +1545,7 @@
         <v>79.7</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>34</v>
       </c>
@@ -1381,7 +1553,7 @@
         <v>74.599999999999994</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>35</v>
       </c>
@@ -1389,7 +1561,7 @@
         <v>83.4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>36</v>
       </c>
@@ -1397,7 +1569,7 @@
         <v>80.400000000000006</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>37</v>
       </c>
@@ -1405,7 +1577,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>38</v>
       </c>
